--- a/AAII_Financials/Quarterly/CTRI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTRI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
   <si>
     <t>CTRI</t>
   </si>
@@ -656,188 +656,195 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E7" s="2">
         <v>46110</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46019</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45928</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45837</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45746</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45655</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45564</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45200</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45109</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="R7" s="2">
         <v>44927</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44836</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>962000</v>
+      </c>
+      <c r="E8" s="3">
         <v>723200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>858600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>850000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>724100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>550100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>717100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>720100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>672100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>528000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>665300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>774900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>805800</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R8" s="3">
         <v>771900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>758500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>706100</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>892800</v>
+      </c>
+      <c r="E9" s="3">
         <v>687400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>778100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>772100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>656300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>529800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>646000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>644300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>611600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>514700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>611400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>687300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>715800</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
@@ -847,50 +854,53 @@
       <c r="S9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>69100</v>
+      </c>
+      <c r="E10" s="3">
         <v>35800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>80500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>78000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>67800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>20300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>71100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>75800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>60500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>13300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>53900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>87600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>90000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
@@ -900,8 +910,11 @@
       <c r="S10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -921,8 +934,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -974,8 +988,11 @@
       <c r="S12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1027,52 +1044,55 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>10500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2300</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>1200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>8300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>221400</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1080,8 +1100,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1089,10 +1112,10 @@
         <v>7800</v>
       </c>
       <c r="E15" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F15" s="3">
         <v>7200</v>
-      </c>
-      <c r="F15" s="3">
-        <v>6700</v>
       </c>
       <c r="G15" s="3">
         <v>6700</v>
@@ -1122,10 +1145,10 @@
         <v>6700</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>5</v>
+        <v>6700</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>5</v>
@@ -1133,8 +1156,11 @@
       <c r="S15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1151,50 +1177,51 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>934800</v>
+      </c>
+      <c r="E17" s="3">
         <v>727900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>819300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>811400</v>
       </c>
-      <c r="G17" s="3">
-        <v>691900</v>
-      </c>
       <c r="H17" s="3">
+        <v>690300</v>
+      </c>
+      <c r="I17" s="3">
         <v>562800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>684000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>676200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>638600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>541600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>639400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>721900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>752600</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>5</v>
       </c>
@@ -1204,50 +1231,53 @@
       <c r="S17" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>39300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>38700</v>
       </c>
-      <c r="G18" s="3">
-        <v>32200</v>
-      </c>
       <c r="H18" s="3">
+        <v>33700</v>
+      </c>
+      <c r="I18" s="3">
         <v>-12700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>33100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>43800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>33500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-13600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>25900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>53000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>53200</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>5</v>
       </c>
@@ -1257,8 +1287,11 @@
       <c r="S18" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1278,50 +1311,51 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-400</v>
-      </c>
-      <c r="H20" s="3">
-        <v>500</v>
       </c>
       <c r="I20" s="3">
         <v>500</v>
       </c>
       <c r="J20" s="3">
+        <v>500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-700</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-900</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1331,52 +1365,55 @@
       <c r="S20" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E21" s="3">
         <v>3000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>46900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>45300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>40800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="J21" s="3">
         <v>39200</v>
       </c>
-      <c r="H21" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="I21" s="3">
-        <v>39200</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>50700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>40800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>32300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>59700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>60800</v>
       </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
+      <c r="Q21" s="3">
+        <v>0</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
@@ -1384,50 +1421,53 @@
       <c r="S21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E22" s="3">
         <v>11800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>25500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>16900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>16700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>16900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>22400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>21300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>22800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>23700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>24800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>23200</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>5</v>
       </c>
@@ -1437,50 +1477,53 @@
       <c r="S22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-17300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>21300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>14300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-31100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>13300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>18200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>11200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-46000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-220200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>26900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>29600</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>5</v>
       </c>
@@ -1490,50 +1533,53 @@
       <c r="S23" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-7800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-9000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-13100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>21800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-20800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-7300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>10000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11000</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>5</v>
       </c>
@@ -1543,8 +1589,11 @@
       <c r="S24" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1596,50 +1645,53 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>30400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>8100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-17900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>11700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-25200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-212800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>16900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>18500</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>5</v>
       </c>
@@ -1649,50 +1701,53 @@
       <c r="S26" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>30200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-17900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>10300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>11700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-25100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-210700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>16200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>17100</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>5</v>
       </c>
@@ -1702,8 +1757,11 @@
       <c r="S27" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1755,8 +1813,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1808,8 +1869,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1861,8 +1925,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1914,50 +1981,53 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>400</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-500</v>
       </c>
       <c r="I32" s="3">
         <v>-500</v>
       </c>
       <c r="J32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>700</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>900</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>5</v>
       </c>
@@ -1967,50 +2037,53 @@
       <c r="S32" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>30200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>8100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-17900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>10300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>11700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-25100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-210700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>16200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>17100</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>5</v>
       </c>
@@ -2020,8 +2093,11 @@
       <c r="S33" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2073,50 +2149,53 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>30200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>8100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-17900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>10300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>11700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-25100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-210700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>16200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>17100</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>5</v>
       </c>
@@ -2126,66 +2205,72 @@
       <c r="S35" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E38" s="2">
         <v>46110</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46019</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45928</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45837</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45746</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45655</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45564</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45200</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45109</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="R38" s="2">
         <v>44927</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44836</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2205,8 +2290,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2226,44 +2312,45 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E41" s="3">
         <v>60300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>126600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>28300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>49000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>52500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>30900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>33400</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2279,8 +2366,11 @@
       <c r="S41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2332,44 +2422,47 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>771500</v>
+      </c>
+      <c r="E43" s="3">
         <v>700900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>709800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>671100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>570600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>479700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>519600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>541600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>627300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>545600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>617300</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>5</v>
       </c>
@@ -2385,8 +2478,11 @@
       <c r="S43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2429,8 +2525,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -2438,8 +2534,11 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2491,44 +2590,47 @@
       <c r="S45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>890000</v>
+      </c>
+      <c r="E46" s="3">
         <v>805600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>881400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>740500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>651900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>536100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>601400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>634600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>723700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>613000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>682900</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>5</v>
       </c>
@@ -2544,52 +2646,55 @@
       <c r="S46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3">
         <v>11500</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3">
         <v>10900</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N47" s="3">
         <v>11900</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -2597,44 +2702,47 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>677100</v>
+      </c>
+      <c r="E48" s="3">
         <v>664200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>667700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>627400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>639900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>640600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>649200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>644100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>685300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>696600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>707400</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
@@ -2650,49 +2758,52 @@
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>719600</v>
+      </c>
+      <c r="E49" s="3">
         <v>728500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>738900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>692700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>701500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>702700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>709200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>722600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>727800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>735600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>744900</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>5</v>
+      <c r="P49" s="3">
+        <v>0</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>5</v>
@@ -2703,8 +2814,11 @@
       <c r="S49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2756,8 +2870,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2809,44 +2926,47 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>84700</v>
+      </c>
+      <c r="E52" s="3">
         <v>85600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>74400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>84900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>84600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>85800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>76800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>83900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>55700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>53400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>38500</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>5</v>
       </c>
@@ -2862,8 +2982,11 @@
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2915,44 +3038,47 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2403200</v>
+      </c>
+      <c r="E54" s="3">
         <v>2321600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2407700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2177300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2107800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1992600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2074400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2112700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2221600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2119300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2189900</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>5</v>
       </c>
@@ -2968,8 +3094,11 @@
       <c r="S54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2989,8 +3118,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3010,44 +3140,45 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>162300</v>
+      </c>
+      <c r="E57" s="3">
         <v>141600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>193600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>146600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>128200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>116000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>125700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>121300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>116600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>114600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>116600</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3063,49 +3194,52 @@
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>83600</v>
+      </c>
+      <c r="E58" s="3">
         <v>80800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>86700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>74200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>68700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>63700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>73200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>69300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>71200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>81900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>86600</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>5</v>
+      <c r="P58" s="3">
+        <v>0</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>5</v>
@@ -3116,44 +3250,47 @@
       <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>66800</v>
+      </c>
+      <c r="E59" s="3">
         <v>58400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>50500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>32100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>32800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>25400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>25000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>21900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>109800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>43700</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
@@ -3169,44 +3306,47 @@
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>490200</v>
+      </c>
+      <c r="E60" s="3">
         <v>428600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>496400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>442200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>379500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>340500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>382300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>386200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>353500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>440200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>420600</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>5</v>
       </c>
@@ -3222,44 +3362,47 @@
       <c r="S60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>863600</v>
+      </c>
+      <c r="E61" s="3">
         <v>860200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>870800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>995500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>995200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>930300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>950600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>992300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1129000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1272300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1237800</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3275,44 +3418,47 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>94700</v>
+      </c>
+      <c r="E62" s="3">
         <v>86800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>83800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>77100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>66700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>65400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>66100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>67900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>69900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>69600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>71100</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>5</v>
       </c>
@@ -3328,8 +3474,11 @@
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3381,8 +3530,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3434,8 +3586,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3487,44 +3642,47 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1527700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1453600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1529300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1587300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1535900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1451400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1514200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1581300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1687200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1917000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1864700</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>5</v>
       </c>
@@ -3540,8 +3698,11 @@
       <c r="S66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3561,8 +3722,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3614,8 +3776,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3667,8 +3832,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3720,8 +3888,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3773,44 +3944,47 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-131800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-137900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-128400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-158600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-160700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-168700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-150700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-161000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-157300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-169000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-144100</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>5</v>
       </c>
@@ -3826,8 +4000,11 @@
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3879,8 +4056,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3932,8 +4112,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3985,44 +4168,47 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>868900</v>
+      </c>
+      <c r="E76" s="3">
         <v>862100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>873000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>585200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>567100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>536500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>555600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>527300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>530400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>197800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>226000</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>5</v>
       </c>
@@ -4038,8 +4224,11 @@
       <c r="S76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4091,108 +4280,114 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E80" s="2">
         <v>46110</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46019</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45928</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45837</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45746</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45655</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45564</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45200</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45109</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q80" s="2">
+      <c r="Q80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="R80" s="2">
         <v>44927</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44836</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>30200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>8100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-17900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>10300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>11700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-25100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-210700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>16200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>17100</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>5</v>
       </c>
@@ -4202,8 +4397,11 @@
       <c r="S81" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4223,8 +4421,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4232,32 +4431,32 @@
         <v>32600</v>
       </c>
       <c r="E83" s="3">
+        <v>32600</v>
+      </c>
+      <c r="F83" s="3">
         <v>32000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>31800</v>
-      </c>
-      <c r="G83" s="3">
-        <v>32800</v>
       </c>
       <c r="H83" s="3">
         <v>32800</v>
       </c>
       <c r="I83" s="3">
+        <v>32800</v>
+      </c>
+      <c r="J83" s="3">
         <v>32600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>34700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>33900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>34900</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
@@ -4276,8 +4475,11 @@
       <c r="S83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4329,8 +4531,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4382,8 +4587,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4435,8 +4643,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4488,8 +4699,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4541,50 +4755,53 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-35000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>83900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-27700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>16700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>61000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>180200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-56600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-26500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>105700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>81300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-71400</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>5</v>
       </c>
@@ -4594,8 +4811,11 @@
       <c r="S89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4615,52 +4835,53 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-20200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-17600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-23600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-20800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-24400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-33200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-19500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-20300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-26300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-27000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-25900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-30500</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -4668,8 +4889,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4721,8 +4945,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4774,50 +5001,53 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-20600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-24000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-21500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-19400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-23200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-30100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-17000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-17700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-24600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-22900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-22800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-28600</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>5</v>
       </c>
@@ -4827,8 +5057,11 @@
       <c r="S94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4848,8 +5081,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4892,8 +5126,8 @@
       <c r="P96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -4901,8 +5135,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4954,8 +5191,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5007,8 +5247,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5060,50 +5303,53 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-10500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>51800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>59900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-27200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-33900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-141800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>86800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>36300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-82000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-52200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>110100</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>5</v>
       </c>
@@ -5113,41 +5359,44 @@
       <c r="S100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
@@ -5166,57 +5415,63 @@
       <c r="S101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-66300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>111900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-12200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>13100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-33800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>21500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>12500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>10400</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
